--- a/public/templates/forms/A-070-AccessAuthorizationList-FORM.xlsx
+++ b/public/templates/forms/A-070-AccessAuthorizationList-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -183,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -236,6 +241,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -701,7 +709,7 @@
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="3" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="34.7" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -748,14 +756,14 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>« One row per authorized person per controlled area. Add a row when access is granted; set Status to Revoked and fill Date Revoked when access ends. The example rows below show the format: replace them. »</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>ID</t>
@@ -807,7 +815,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>AUTH-001</t>
@@ -859,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>AUTH-002</t>
@@ -911,7 +919,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>AUTH-003</t>
@@ -1054,7 +1062,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Total entries</t>
@@ -1062,7 +1070,6 @@
       </c>
       <c r="C24" s="12">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1073,10 +1080,9 @@
       </c>
       <c r="C25" s="12">
         <f>COUNTIF(H12:H21,"Active")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
+      </c>
+    </row>
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Suspended</t>
@@ -1084,7 +1090,6 @@
       </c>
       <c r="C26" s="12">
         <f>COUNTIF(H12:H21,"Suspended")</f>
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -1095,10 +1100,9 @@
       </c>
       <c r="C27" s="12">
         <f>COUNTIF(H12:H21,"Revoked")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
+      </c>
+    </row>
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Past due for review</t>
@@ -1106,7 +1110,6 @@
       </c>
       <c r="C28" s="12">
         <f>COUNTIF(J12:J21,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -1180,7 +1183,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="50.5" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
           <t>[Approving official / title]</t>
@@ -1190,7 +1193,7 @@
       <c r="C39" s="10" t="inlineStr"/>
       <c r="D39" s="10" t="inlineStr"/>
     </row>
-    <row r="40">
+    <row r="40" ht="34.7" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
           <t>[Owner role]</t>
@@ -1251,7 +1254,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="50.5" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): Build-order item #33; maintained under the Physical Access Control Policy. Classification raised to Confidential because entries name individuals (PII). Columns reshaped from the generic register into an authorization roster: individual, area, credential, authorizer, issue/revoke dates, status. Example rows AUTH-001..003 show an active and a revoked entry: replace them. Agency-supplied values left in brackets.</t>
@@ -1299,8 +1302,8 @@
       <formula1>"Active,Suspended,Revoked"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1329,7 +1332,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="3" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>How to use: this register lists who is authorized to enter each controlled area, the credential they hold, who authorized it, and when access was granted and removed. Fill the header block on the Register tab, replace every [BRACKETED] field, add one row per authorization, and delete every « » note before publishing.</t>
@@ -1339,7 +1342,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1375,7 +1378,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1397,7 +1400,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Authorized Individual (Name &amp; Role)</t>
@@ -1501,10 +1504,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D12" s="20">
+        <v>46082</v>
       </c>
     </row>
     <row r="13">
@@ -1523,10 +1524,8 @@
           <t>When applicable</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
+      <c r="D13" s="20">
+        <v>46266</v>
       </c>
     </row>
     <row r="14">
@@ -1567,13 +1566,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="D15" s="20">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Next Review Due</t>
@@ -1589,13 +1586,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="D16" s="20">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>« Summary on the Register tab counts entries by status and flags any past their Next Review Due date. Extend the COUNTIF formulas if you add status values. »</t>
@@ -1677,7 +1672,7 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>